--- a/Data/fondos_selected.xlsx
+++ b/Data/fondos_selected.xlsx
@@ -1544,13 +1544,13 @@
         <v>163</v>
       </c>
       <c r="G9">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="H9">
-        <v>4.87</v>
+        <v>4.85</v>
       </c>
       <c r="I9">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="J9">
         <v>0.66</v>
@@ -1580,7 +1580,7 @@
         <v>-4.64</v>
       </c>
       <c r="S9">
-        <v>11.95</v>
+        <v>11.94</v>
       </c>
       <c r="T9">
         <v>0.3</v>
@@ -1840,10 +1840,10 @@
         <v>159</v>
       </c>
       <c r="G13">
-        <v>8.56</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H13">
-        <v>7.34</v>
+        <v>7.29</v>
       </c>
       <c r="I13" t="s">
         <v>184</v>
@@ -1876,7 +1876,7 @@
         <v>185</v>
       </c>
       <c r="S13">
-        <v>13.59</v>
+        <v>13.57</v>
       </c>
       <c r="T13">
         <v>0.75</v>
@@ -2062,13 +2062,13 @@
         <v>166</v>
       </c>
       <c r="G16">
-        <v>3.28</v>
+        <v>4.46</v>
       </c>
       <c r="H16">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="I16">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="J16">
         <v>2.54</v>
@@ -2098,7 +2098,7 @@
         <v>-8.630000000000001</v>
       </c>
       <c r="S16">
-        <v>118.25</v>
+        <v>118.3</v>
       </c>
       <c r="T16">
         <v>0.25</v>
@@ -2284,13 +2284,13 @@
         <v>75</v>
       </c>
       <c r="G19">
-        <v>4.49</v>
+        <v>4.87</v>
       </c>
       <c r="H19">
-        <v>7.99</v>
+        <v>7.98</v>
       </c>
       <c r="I19">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="J19">
         <v>2.56</v>
@@ -2320,7 +2320,7 @@
         <v>-16.91</v>
       </c>
       <c r="S19">
-        <v>159.04</v>
+        <v>158.98</v>
       </c>
       <c r="T19">
         <v>1</v>
@@ -2358,13 +2358,13 @@
         <v>159</v>
       </c>
       <c r="G20">
-        <v>8.15</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H20">
-        <v>5.94</v>
+        <v>5.71</v>
       </c>
       <c r="I20">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="J20">
         <v>3.03</v>
@@ -2394,7 +2394,7 @@
         <v>-5.06</v>
       </c>
       <c r="S20">
-        <v>9.31</v>
+        <v>9.25</v>
       </c>
       <c r="T20">
         <v>1.35</v>
@@ -2506,13 +2506,13 @@
         <v>170</v>
       </c>
       <c r="G22">
-        <v>4.7</v>
+        <v>5.29</v>
       </c>
       <c r="H22">
-        <v>5.76</v>
+        <v>5.78</v>
       </c>
       <c r="I22">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
       <c r="J22">
         <v>1.61</v>
@@ -2542,7 +2542,7 @@
         <v>-4.49</v>
       </c>
       <c r="S22">
-        <v>130.1</v>
+        <v>130.16</v>
       </c>
       <c r="T22">
         <v>0.835</v>
@@ -2728,13 +2728,13 @@
         <v>172</v>
       </c>
       <c r="G25">
-        <v>-7.52</v>
+        <v>-3.9</v>
       </c>
       <c r="H25">
-        <v>-1.76</v>
+        <v>-1.94</v>
       </c>
       <c r="I25">
-        <v>-11.37</v>
+        <v>-11.44</v>
       </c>
       <c r="J25">
         <v>9.640000000000001</v>
@@ -2764,7 +2764,7 @@
         <v>-49.84</v>
       </c>
       <c r="S25">
-        <v>136.92</v>
+        <v>136.17</v>
       </c>
       <c r="T25">
         <v>0.16</v>
@@ -2950,13 +2950,13 @@
         <v>175</v>
       </c>
       <c r="G28">
-        <v>-0.18</v>
+        <v>-2.37</v>
       </c>
       <c r="H28">
-        <v>4.31</v>
+        <v>3.61</v>
       </c>
       <c r="I28">
-        <v>-5.55</v>
+        <v>-5.37</v>
       </c>
       <c r="J28">
         <v>20.33</v>
@@ -2986,7 +2986,7 @@
         <v>-50.34</v>
       </c>
       <c r="S28">
-        <v>138.57</v>
+        <v>135.78</v>
       </c>
       <c r="T28">
         <v>0.6</v>
@@ -3098,13 +3098,13 @@
         <v>177</v>
       </c>
       <c r="G30">
-        <v>39.55</v>
+        <v>40.58</v>
       </c>
       <c r="H30">
-        <v>20.61</v>
+        <v>20.49</v>
       </c>
       <c r="I30">
-        <v>20.1</v>
+        <v>19.84</v>
       </c>
       <c r="J30">
         <v>12.1</v>
@@ -3134,7 +3134,7 @@
         <v>-17.39</v>
       </c>
       <c r="S30">
-        <v>170.31</v>
+        <v>169.77</v>
       </c>
       <c r="T30">
         <v>0.125</v>
@@ -3397,13 +3397,13 @@
         <v>159</v>
       </c>
       <c r="G34">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="H34">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
       <c r="I34">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="J34">
         <v>1.11</v>
@@ -3433,7 +3433,7 @@
         <v>-3.34</v>
       </c>
       <c r="S34">
-        <v>12.85</v>
+        <v>12.84</v>
       </c>
       <c r="T34">
         <v>1.2</v>
@@ -3545,13 +3545,13 @@
         <v>181</v>
       </c>
       <c r="G36">
-        <v>3.62</v>
+        <v>4.02</v>
       </c>
       <c r="H36">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="I36">
-        <v>5.12</v>
+        <v>5.14</v>
       </c>
       <c r="J36">
         <v>1.29</v>
@@ -3581,7 +3581,7 @@
         <v>-2.59</v>
       </c>
       <c r="S36">
-        <v>130.77</v>
+        <v>130.56</v>
       </c>
       <c r="T36">
         <v>1.2</v>
@@ -3619,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>8.07</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H37">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="I37">
-        <v>5.93</v>
+        <v>5.99</v>
       </c>
       <c r="J37">
         <v>1.28</v>
@@ -3655,7 +3655,7 @@
         <v>-3.42</v>
       </c>
       <c r="S37">
-        <v>1799.6</v>
+        <v>1799.11</v>
       </c>
       <c r="T37">
         <v>1.75</v>
